--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92564202884</v>
+        <v>46157.93084110524</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93084110524</v>
+        <v>46157.93162330272</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93162330272</v>
+        <v>46157.93396308381</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93396308381</v>
+        <v>46157.93713633457</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93713633457</v>
+        <v>46158.28212779545</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28212779545</v>
+        <v>46158.29673976661</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29673976661</v>
+        <v>46158.298101696</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.298101696</v>
+        <v>46158.33383647365</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33383647365</v>
+        <v>46158.36852107276</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36852107276</v>
+        <v>46158.37283809581</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
